--- a/Excel/SceneInfo.xlsx
+++ b/Excel/SceneInfo.xlsx
@@ -17,10 +17,10 @@
     <t>&lt;/summary&gt;</t>
   </si>
   <si>
-    <t>id:int</t>
-  </si>
-  <si>
-    <t>key:string</t>
+    <t>Id:int</t>
+  </si>
+  <si>
+    <t>Key:string</t>
   </si>
   <si>
     <t>LoadMode:SceneLoadType</t>
@@ -359,10 +359,10 @@
     <row r="3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
